--- a/docs/A2_llave_class_uso/Propuesta_clasificacion_llave.xlsx
+++ b/docs/A2_llave_class_uso/Propuesta_clasificacion_llave.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jesus\Work\CR\Github\PGBM_actividad_1_diagnostico\docs\A2_llave_class_uso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF026A2E-30B5-4539-A0C7-BFDF502D2C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B87F34-2FF9-4A7F-96A5-A6DF35F138D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6258B49D-24C2-44E4-9222-D2FE7227FFE6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>Nivel 0</t>
   </si>
@@ -83,12 +83,6 @@
     <t>Nivel 2 operativo</t>
   </si>
   <si>
-    <t>Bosque</t>
-  </si>
-  <si>
-    <t>Bosques</t>
-  </si>
-  <si>
     <t>Bosques verdes / latifoliados húmedos</t>
   </si>
   <si>
@@ -104,17 +98,26 @@
     <t>Palma aceitera</t>
   </si>
   <si>
-    <t>Zonas agrícolas</t>
-  </si>
-  <si>
     <t>Musáceas — banano/plátano</t>
+  </si>
+  <si>
+    <t>Bosque/Tierras forestales</t>
+  </si>
+  <si>
+    <t>Plantaciones forestales</t>
+  </si>
+  <si>
+    <t>Zonas agrícolas/no arboreas</t>
+  </si>
+  <si>
+    <t>Cacao</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,13 +133,68 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -151,13 +209,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -165,6 +259,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCCFF99"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -493,12 +592,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50BC712D-BF6A-4CE6-A7BF-0EBC5C98357E}">
-  <dimension ref="A16:C33"/>
+  <dimension ref="A16:C39"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="31.5546875" customWidth="1"/>
+    <col min="3" max="3" width="46.6640625" customWidth="1"/>
     <col min="4" max="4" width="41" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -514,173 +613,155 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="2" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="2" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="4"/>
+      <c r="B22" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="C23" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="2" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="2" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+      <c r="B26" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="2" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="5"/>
+      <c r="B31" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+      <c r="B32" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+      <c r="B33" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C33" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C39" s="2"/>
+    </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A23:A33"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="B23:B25"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>